--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -398,7 +398,7 @@
     <t>MSTC LIMITED  •  LIVE SEARCH   (results grouped by the value you typed, each group totalled, TOTAL MATCHED beneath them, the misses greyed in a REMAINING block, a GRAND TOTAL of both at the foot)</t>
   </si>
   <si>
-    <t>HOW TO USE  ▶  click the yellow box B3 and type - a lot number (1874), part of one (187), a buyer (NATIONAL), part of a buyer name, a lot name (COPPER).   •   WILDCARD / MATCH ANY - separate values with a comma or a slash:   1874, 1923, OMKAR   or   1874 / 1923    - and every lot containing ANY of them lights up.   •   COLUMN SEARCHES - type above any column header in row 4; comma or slash means ANY value in that column, * matches any text and ? matches one character.  Filters entered in different columns are combined as ALL.   •   FACETED / FILTERED - separate them with + or &amp;:   NATIONAL + COPPER   - and a lot lights up only if it matches EVERY facet.   •   the two mix:   OMKAR, STERLING + COPPER   = (OMKAR or STERLING) and COPPER.   Up to 8 values, empty ones ignored, spaces around a separator are fine.  •   THE RESULT IS GROUPED BY THE VALUE YOU TYPED: every value gets its own block of lots with a shaded ∑ total row beneath it, then a blue TOTAL MATCHED row adds every group up at once - the grand total of the rows your search actually hit, sitting right beneath them.  Under that a greyed REMAINING block holds the lots that did not match, with its own total, and the green GRAND TOTAL of both sits at the foot.  A lot matching two values is counted under the first one only, so TOTAL MATCHED + REMAINING always equals GRAND TOTAL, and with nothing typed the matched row is the whole list.   •   clear the box and all 37 come back in one ALL LOTS block.   •   cell F3 narrows what the text is looked for in (lot no. + buyer + name by default).   •   matching is contains, not case sensitive.   •   nothing here is typed in: every figure is a live link to Final Calculation Sheet.   •   columns AK..CU are hidden helpers.</t>
+    <t>HOW TO USE  ▶  click the yellow box B3 and type - a lot number (1874), part of one (187), a buyer (NATIONAL), part of a buyer name, a lot name (COPPER).   •   WILDCARD / MATCH ANY - separate values with a comma or a slash:   1874, 1923, OMKAR   or   1874 / 1923    - and every lot containing ANY of them lights up.   •   COLUMN SEARCHES - type above any column header in row 4; comma or slash means ANY value in that column, * matches any text and ? matches one character.  Filters entered in different columns are combined as ALL.   •   FACETED / FILTERED - separate them with + or &amp;:   NATIONAL + COPPER   - and a lot lights up only if it matches EVERY facet.   •   the two mix:   OMKAR, STERLING + COPPER   = (OMKAR or STERLING) and COPPER.   Up to 8 values, empty ones ignored, spaces around a separator are fine.  •   THE RESULT IS GROUPED BY THE VALUE YOU TYPED: every value gets its own block of lots with a shaded ∑ total row beneath it, then a blue TOTAL MATCHED row adds every group up at once - the grand total of the rows your search actually hit, sitting right beneath them.  Under that a greyed REMAINING block holds the lots that did not match, with its own total, and the green GRAND TOTAL of both sits at the foot.  A lot matching two values is counted under the first one only, so TOTAL MATCHED + REMAINING always equals GRAND TOTAL, and with nothing typed the matched row is the whole list.   •   clear the box and all 37 come back in one ALL LOTS block.   •   cell F3 narrows what the text is looked for in (lot no. + buyer + name by default).   •   matching is contains, not case sensitive.   •   nothing here is typed in: every figure is a live link to Final Calculation Sheet.   •   columns AK..CU are hidden helpers.   •   use the +/- outline control above columns D:H to expand/collapse Lot Name through Rate under Buyer.</t>
   </si>
   <si>
     <t>🔍  SEARCH  ▸</t>
@@ -6078,22 +6078,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
+    <outlinePr summaryRight="1" summaryBelow="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CU54"/>
-  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="34" width="13.42578125" customWidth="1"/>
@@ -6101,7 +6102,7 @@
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:99" ht="30" customHeight="1" ns3:dyDescent="0.25">
+    <row r="1" spans="1:99" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
         <v>122</v>
       </c>
@@ -6140,7 +6141,7 @@
       <c r="AH1" s="77"/>
       <c r="AI1" s="77"/>
     </row>
-    <row r="2" spans="1:99" ht="44.1" customHeight="1" ns3:dyDescent="0.25">
+    <row r="2" spans="1:99" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="76" t="s">
         <v>123</v>
       </c>
@@ -6179,7 +6180,7 @@
       <c r="AH2" s="77"/>
       <c r="AI2" s="77"/>
     </row>
-    <row r="3" spans="1:99" ht="30" customHeight="1" ns3:dyDescent="0.25">
+    <row r="3" spans="1:99" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>124</v>
       </c>
@@ -6247,7 +6248,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:99" ht="30" customHeight="1" ns3:dyDescent="0.25">
+    <row r="4" spans="1:99" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61"/>
       <c r="B4" s="61"/>
       <c r="C4" s="61"/>
@@ -6338,7 +6339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:99" ht="44.1" customHeight="1" ns3:dyDescent="0.25">
+    <row r="5" spans="1:99" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
         <v>133</v>
       </c>
@@ -6679,7 +6680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="6" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="67">
         <f>IF($BJ5&gt;0,INDEX($BA$5:$BA$41,MATCH(5,$BB$5:$BB$41,0)),IF(OR($BI5=1,$BL5=1,$BH5&gt;0),"∑",""))</f>
         <v>1</v>
@@ -7051,7 +7052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="7" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67">
         <f>IF($BJ6&gt;0,INDEX($BA$5:$BA$41,MATCH(6,$BB$5:$BB$41,0)),IF(OR($BI6=1,$BL6=1,$BH6&gt;0),"∑",""))</f>
         <v>2</v>
@@ -7423,7 +7424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="8" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="67">
         <f>IF($BJ7&gt;0,INDEX($BA$5:$BA$41,MATCH(7,$BB$5:$BB$41,0)),IF(OR($BI7=1,$BL7=1,$BH7&gt;0),"∑",""))</f>
         <v>3</v>
@@ -7794,7 +7795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="9" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="67">
         <f>IF($BJ8&gt;0,INDEX($BA$5:$BA$41,MATCH(8,$BB$5:$BB$41,0)),IF(OR($BI8=1,$BL8=1,$BH8&gt;0),"∑",""))</f>
         <v>4</v>
@@ -8166,7 +8167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="10" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="str">
         <f>IF($BJ9&gt;0,INDEX($BA$5:$BA$41,MATCH(9,$BB$5:$BB$41,0)),IF(OR($BI9=1,$BL9=1,$BH9&gt;0),"∑",""))</f>
         <v>∑</v>
@@ -8503,7 +8504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="11" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
         <f>IF($BJ10&gt;0,INDEX($BA$5:$BA$41,MATCH(10,$BB$5:$BB$41,0)),IF(OR($BI10=1,$BL10=1,$BH10&gt;0),"∑",""))</f>
         <v>1</v>
@@ -8840,7 +8841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="12" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
         <f>IF($BJ11&gt;0,INDEX($BA$5:$BA$41,MATCH(11,$BB$5:$BB$41,0)),IF(OR($BI11=1,$BL11=1,$BH11&gt;0),"∑",""))</f>
         <v>2</v>
@@ -9177,7 +9178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="13" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
         <f>IF($BJ12&gt;0,INDEX($BA$5:$BA$41,MATCH(12,$BB$5:$BB$41,0)),IF(OR($BI12=1,$BL12=1,$BH12&gt;0),"∑",""))</f>
         <v>3</v>
@@ -9514,7 +9515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="14" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
         <f>IF($BJ13&gt;0,INDEX($BA$5:$BA$41,MATCH(13,$BB$5:$BB$41,0)),IF(OR($BI13=1,$BL13=1,$BH13&gt;0),"∑",""))</f>
         <v>4</v>
@@ -9839,7 +9840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="15" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
         <f>IF($BJ14&gt;0,INDEX($BA$5:$BA$41,MATCH(14,$BB$5:$BB$41,0)),IF(OR($BI14=1,$BL14=1,$BH14&gt;0),"∑",""))</f>
         <v>5</v>
@@ -10164,7 +10165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="16" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67" t="str">
         <f>IF($BJ15&gt;0,INDEX($BA$5:$BA$41,MATCH(15,$BB$5:$BB$41,0)),IF(OR($BI15=1,$BL15=1,$BH15&gt;0),"∑",""))</f>
         <v>∑</v>
@@ -10489,7 +10490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="17" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67" t="str">
         <f>IF($BJ16&gt;0,INDEX($BA$5:$BA$41,MATCH(16,$BB$5:$BB$41,0)),IF(OR($BI16=1,$BL16=1,$BH16&gt;0),"∑",""))</f>
         <v>∑</v>
@@ -10814,7 +10815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="18" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
         <f>IF($BJ17&gt;0,INDEX($BA$5:$BA$41,MATCH(17,$BB$5:$BB$41,0)),IF(OR($BI17=1,$BL17=1,$BH17&gt;0),"∑",""))</f>
         <v>1</v>
@@ -11139,7 +11140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="19" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
         <f>IF($BJ18&gt;0,INDEX($BA$5:$BA$41,MATCH(18,$BB$5:$BB$41,0)),IF(OR($BI18=1,$BL18=1,$BH18&gt;0),"∑",""))</f>
         <v>2</v>
@@ -11464,7 +11465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="20" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="67">
         <f>IF($BJ19&gt;0,INDEX($BA$5:$BA$41,MATCH(19,$BB$5:$BB$41,0)),IF(OR($BI19=1,$BL19=1,$BH19&gt;0),"∑",""))</f>
         <v>3</v>
@@ -11789,7 +11790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="21" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
         <f>IF($BJ20&gt;0,INDEX($BA$5:$BA$41,MATCH(20,$BB$5:$BB$41,0)),IF(OR($BI20=1,$BL20=1,$BH20&gt;0),"∑",""))</f>
         <v>4</v>
@@ -12114,7 +12115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="22" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
         <f>IF($BJ21&gt;0,INDEX($BA$5:$BA$41,MATCH(21,$BB$5:$BB$41,0)),IF(OR($BI21=1,$BL21=1,$BH21&gt;0),"∑",""))</f>
         <v>5</v>
@@ -12439,7 +12440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="23" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
         <f>IF($BJ22&gt;0,INDEX($BA$5:$BA$41,MATCH(22,$BB$5:$BB$41,0)),IF(OR($BI22=1,$BL22=1,$BH22&gt;0),"∑",""))</f>
         <v>6</v>
@@ -12764,7 +12765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="24" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
         <f>IF($BJ23&gt;0,INDEX($BA$5:$BA$41,MATCH(23,$BB$5:$BB$41,0)),IF(OR($BI23=1,$BL23=1,$BH23&gt;0),"∑",""))</f>
         <v>7</v>
@@ -13089,7 +13090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="25" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67">
         <f>IF($BJ24&gt;0,INDEX($BA$5:$BA$41,MATCH(24,$BB$5:$BB$41,0)),IF(OR($BI24=1,$BL24=1,$BH24&gt;0),"∑",""))</f>
         <v>8</v>
@@ -13414,7 +13415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="26" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67">
         <f>IF($BJ25&gt;0,INDEX($BA$5:$BA$41,MATCH(25,$BB$5:$BB$41,0)),IF(OR($BI25=1,$BL25=1,$BH25&gt;0),"∑",""))</f>
         <v>9</v>
@@ -13739,7 +13740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="27" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67">
         <f>IF($BJ26&gt;0,INDEX($BA$5:$BA$41,MATCH(26,$BB$5:$BB$41,0)),IF(OR($BI26=1,$BL26=1,$BH26&gt;0),"∑",""))</f>
         <v>10</v>
@@ -14064,7 +14065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="28" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67">
         <f>IF($BJ27&gt;0,INDEX($BA$5:$BA$41,MATCH(27,$BB$5:$BB$41,0)),IF(OR($BI27=1,$BL27=1,$BH27&gt;0),"∑",""))</f>
         <v>11</v>
@@ -14389,7 +14390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="29" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67">
         <f>IF($BJ28&gt;0,INDEX($BA$5:$BA$41,MATCH(28,$BB$5:$BB$41,0)),IF(OR($BI28=1,$BL28=1,$BH28&gt;0),"∑",""))</f>
         <v>12</v>
@@ -14714,7 +14715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="30" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="67">
         <f>IF($BJ29&gt;0,INDEX($BA$5:$BA$41,MATCH(29,$BB$5:$BB$41,0)),IF(OR($BI29=1,$BL29=1,$BH29&gt;0),"∑",""))</f>
         <v>13</v>
@@ -15039,7 +15040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="31" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67">
         <f>IF($BJ30&gt;0,INDEX($BA$5:$BA$41,MATCH(30,$BB$5:$BB$41,0)),IF(OR($BI30=1,$BL30=1,$BH30&gt;0),"∑",""))</f>
         <v>14</v>
@@ -15364,7 +15365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="32" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
         <f>IF($BJ31&gt;0,INDEX($BA$5:$BA$41,MATCH(31,$BB$5:$BB$41,0)),IF(OR($BI31=1,$BL31=1,$BH31&gt;0),"∑",""))</f>
         <v>15</v>
@@ -15689,7 +15690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="33" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
         <f>IF($BJ32&gt;0,INDEX($BA$5:$BA$41,MATCH(32,$BB$5:$BB$41,0)),IF(OR($BI32=1,$BL32=1,$BH32&gt;0),"∑",""))</f>
         <v>16</v>
@@ -16014,7 +16015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="34" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
         <f>IF($BJ33&gt;0,INDEX($BA$5:$BA$41,MATCH(33,$BB$5:$BB$41,0)),IF(OR($BI33=1,$BL33=1,$BH33&gt;0),"∑",""))</f>
         <v>17</v>
@@ -16339,7 +16340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="35" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
         <f>IF($BJ34&gt;0,INDEX($BA$5:$BA$41,MATCH(34,$BB$5:$BB$41,0)),IF(OR($BI34=1,$BL34=1,$BH34&gt;0),"∑",""))</f>
         <v>18</v>
@@ -16664,7 +16665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="36" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
         <f>IF($BJ35&gt;0,INDEX($BA$5:$BA$41,MATCH(35,$BB$5:$BB$41,0)),IF(OR($BI35=1,$BL35=1,$BH35&gt;0),"∑",""))</f>
         <v>19</v>
@@ -16989,7 +16990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="37" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67">
         <f>IF($BJ36&gt;0,INDEX($BA$5:$BA$41,MATCH(36,$BB$5:$BB$41,0)),IF(OR($BI36=1,$BL36=1,$BH36&gt;0),"∑",""))</f>
         <v>20</v>
@@ -17314,7 +17315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="38" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67">
         <f>IF($BJ37&gt;0,INDEX($BA$5:$BA$41,MATCH(37,$BB$5:$BB$41,0)),IF(OR($BI37=1,$BL37=1,$BH37&gt;0),"∑",""))</f>
         <v>21</v>
@@ -17639,7 +17640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="39" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="67">
         <f>IF($BJ38&gt;0,INDEX($BA$5:$BA$41,MATCH(38,$BB$5:$BB$41,0)),IF(OR($BI38=1,$BL38=1,$BH38&gt;0),"∑",""))</f>
         <v>22</v>
@@ -17964,7 +17965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="40" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="67">
         <f>IF($BJ39&gt;0,INDEX($BA$5:$BA$41,MATCH(39,$BB$5:$BB$41,0)),IF(OR($BI39=1,$BL39=1,$BH39&gt;0),"∑",""))</f>
         <v>23</v>
@@ -18289,7 +18290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="41" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="67">
         <f>IF($BJ40&gt;0,INDEX($BA$5:$BA$41,MATCH(40,$BB$5:$BB$41,0)),IF(OR($BI40=1,$BL40=1,$BH40&gt;0),"∑",""))</f>
         <v>24</v>
@@ -18614,7 +18615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="42" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="67">
         <f>IF($BJ41&gt;0,INDEX($BA$5:$BA$41,MATCH(41,$BB$5:$BB$41,0)),IF(OR($BI41=1,$BL41=1,$BH41&gt;0),"∑",""))</f>
         <v>25</v>
@@ -18776,7 +18777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="43" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="67">
         <f>IF($BJ42&gt;0,INDEX($BA$5:$BA$41,MATCH(42,$BB$5:$BB$41,0)),IF(OR($BI42=1,$BL42=1,$BH42&gt;0),"∑",""))</f>
         <v>26</v>
@@ -18938,7 +18939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="44" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="67">
         <f>IF($BJ43&gt;0,INDEX($BA$5:$BA$41,MATCH(43,$BB$5:$BB$41,0)),IF(OR($BI43=1,$BL43=1,$BH43&gt;0),"∑",""))</f>
         <v>27</v>
@@ -19100,7 +19101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="45" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="67">
         <f>IF($BJ44&gt;0,INDEX($BA$5:$BA$41,MATCH(44,$BB$5:$BB$41,0)),IF(OR($BI44=1,$BL44=1,$BH44&gt;0),"∑",""))</f>
         <v>28</v>
@@ -19262,7 +19263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="46" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="67" t="str">
         <f>IF($BJ45&gt;0,INDEX($BA$5:$BA$41,MATCH(45,$BB$5:$BB$41,0)),IF(OR($BI45=1,$BL45=1,$BH45&gt;0),"∑",""))</f>
         <v>∑</v>
@@ -19424,7 +19425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="47" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="67" t="str">
         <f>IF($BJ46&gt;0,INDEX($BA$5:$BA$41,MATCH(46,$BB$5:$BB$41,0)),IF(OR($BI46=1,$BL46=1,$BH46&gt;0),"∑",""))</f>
         <v>∑</v>
@@ -19586,7 +19587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="48" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="67" t="str">
         <f>IF($BJ47&gt;0,INDEX($BA$5:$BA$41,MATCH(47,$BB$5:$BB$41,0)),IF(OR($BI47=1,$BL47=1,$BH47&gt;0),"∑",""))</f>
         <v/>
@@ -19748,7 +19749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="49" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="67" t="str">
         <f>IF($BJ48&gt;0,INDEX($BA$5:$BA$41,MATCH(48,$BB$5:$BB$41,0)),IF(OR($BI48=1,$BL48=1,$BH48&gt;0),"∑",""))</f>
         <v/>
@@ -19910,7 +19911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="50" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="67" t="str">
         <f>IF($BJ49&gt;0,INDEX($BA$5:$BA$41,MATCH(49,$BB$5:$BB$41,0)),IF(OR($BI49=1,$BL49=1,$BH49&gt;0),"∑",""))</f>
         <v/>
@@ -20072,7 +20073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="51" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="67" t="str">
         <f>IF($BJ50&gt;0,INDEX($BA$5:$BA$41,MATCH(50,$BB$5:$BB$41,0)),IF(OR($BI50=1,$BL50=1,$BH50&gt;0),"∑",""))</f>
         <v/>
@@ -20234,7 +20235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="52" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="67" t="str">
         <f>IF($BJ51&gt;0,INDEX($BA$5:$BA$41,MATCH(51,$BB$5:$BB$41,0)),IF(OR($BI51=1,$BL51=1,$BH51&gt;0),"∑",""))</f>
         <v/>
@@ -20396,7 +20397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="53" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="67" t="str">
         <f>IF($BJ52&gt;0,INDEX($BA$5:$BA$41,MATCH(52,$BB$5:$BB$41,0)),IF(OR($BI52=1,$BL52=1,$BH52&gt;0),"∑",""))</f>
         <v/>
@@ -20558,7 +20559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:99" ht="15" customHeight="1" ns3:dyDescent="0.25">
+    <row r="54" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="67" t="str">
         <f>IF($BJ53&gt;0,INDEX($BA$5:$BA$41,MATCH(53,$BB$5:$BB$41,0)),IF(OR($BI53=1,$BL53=1,$BH53&gt;0),"∑",""))</f>
         <v/>
@@ -20749,7 +20750,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F3" ns2:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="F3" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$AO$4:$AO$9</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="A4:AI4" promptTitle="Column wildcard search" prompt="Type text; comma or / means ANY. Use * for any text or ? for one character.">

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20361"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <ns2:absPath url="C:\Users\S.M.C\Downloads\"/>
+      <x15ac:absPath url="C:\Users\S.M.C\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D8CAA5-FA05-4AFF-A696-DFAD20822EA2}" ns4:coauthVersionLast="36" ns4:coauthVersionMax="36" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D8CAA5-FA05-4AFF-A696-DFAD20822EA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6078,7 +6078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
     <outlinePr summaryRight="1" summaryBelow="1"/>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6096,8 +6096,9 @@
     <col min="7" max="7" width="11" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="34" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6098,7 +6098,8 @@
     <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="13.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="34" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6099,7 +6099,8 @@
     <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="13.42578125" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="13.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="34" width="13.42578125" customWidth="1"/>
+    <col min="13" max="16" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6100,7 +6100,9 @@
     <col min="11" max="11" width="13.42578125" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="13.42578125" customWidth="1" outlineLevel="1"/>
     <col min="13" max="16" width="13.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="34" width="13.42578125" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6102,7 +6102,9 @@
     <col min="13" max="16" width="13.42578125" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="13.42578125" customWidth="1"/>
     <col min="18" max="18" width="13.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="34" width="13.42578125" customWidth="1"/>
+    <col min="19" max="20" width="13.42578125" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6104,7 +6104,9 @@
     <col min="18" max="18" width="13.42578125" customWidth="1" outlineLevel="1"/>
     <col min="19" max="20" width="13.42578125" customWidth="1"/>
     <col min="21" max="21" width="13.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="34" width="13.42578125" customWidth="1"/>
+    <col min="22" max="23" width="13.42578125" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -6106,7 +6106,9 @@
     <col min="21" max="21" width="13.42578125" customWidth="1" outlineLevel="1"/>
     <col min="22" max="23" width="13.42578125" customWidth="1"/>
     <col min="24" max="24" width="13.42578125" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="34" width="13.42578125" customWidth="1"/>
+    <col min="25" max="26" width="13.42578125" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="34" width="13.42578125" customWidth="1"/>
     <col min="35" max="35" width="13" customWidth="1"/>
     <col min="37" max="99" width="12" hidden="1" customWidth="1"/>
   </cols>

--- a/07.09.2026.xlsx
+++ b/07.09.2026.xlsx
@@ -398,7 +398,7 @@
     <t>MSTC LIMITED  •  LIVE SEARCH   (results grouped by the value you typed, each group totalled, TOTAL MATCHED beneath them, the misses greyed in a REMAINING block, a GRAND TOTAL of both at the foot)</t>
   </si>
   <si>
-    <t>HOW TO USE  ▶  click the yellow box B3 and type - a lot number (1874), part of one (187), a buyer (NATIONAL), part of a buyer name, a lot name (COPPER).   •   WILDCARD / MATCH ANY - separate values with a comma or a slash:   1874, 1923, OMKAR   or   1874 / 1923    - and every lot containing ANY of them lights up.   •   COLUMN SEARCHES - type above any column header in row 4; comma or slash means ANY value in that column, * matches any text and ? matches one character.  Filters entered in different columns are combined as ALL.   •   FACETED / FILTERED - separate them with + or &amp;:   NATIONAL + COPPER   - and a lot lights up only if it matches EVERY facet.   •   the two mix:   OMKAR, STERLING + COPPER   = (OMKAR or STERLING) and COPPER.   Up to 8 values, empty ones ignored, spaces around a separator are fine.  •   THE RESULT IS GROUPED BY THE VALUE YOU TYPED: every value gets its own block of lots with a shaded ∑ total row beneath it, then a blue TOTAL MATCHED row adds every group up at once - the grand total of the rows your search actually hit, sitting right beneath them.  Under that a greyed REMAINING block holds the lots that did not match, with its own total, and the green GRAND TOTAL of both sits at the foot.  A lot matching two values is counted under the first one only, so TOTAL MATCHED + REMAINING always equals GRAND TOTAL, and with nothing typed the matched row is the whole list.   •   clear the box and all 37 come back in one ALL LOTS block.   •   cell F3 narrows what the text is looked for in (lot no. + buyer + name by default).   •   matching is contains, not case sensitive.   •   nothing here is typed in: every figure is a live link to Final Calculation Sheet.   •   columns AK..CU are hidden helpers.   •   use the +/- outline control above columns D:H to expand/collapse Lot Name through Rate under Buyer.</t>
+    <t>HOW TO USE  ▶  click the yellow box B3 and type - a lot number (1874), part of one (187), a buyer (NATIONAL), part of a buyer name, a lot name (COPPER).   •   WILDCARD / MATCH ANY - separate values with a comma or a slash:   1874, 1923, OMKAR   or   1874 / 1923    - and every lot containing ANY of them lights up.   •   COLUMN SEARCHES - type above any column header in row 4; comma or slash means ANY value in that column, * matches any text and ? matches one character.  Filters entered in different columns are combined as ALL.   •   FACETED / FILTERED - separate them with + or &amp;:   NATIONAL + COPPER   - and a lot lights up only if it matches EVERY facet.   •   the two mix:   OMKAR, STERLING + COPPER   = (OMKAR or STERLING) and COPPER.   Up to 8 values, empty ones ignored, spaces around a separator are fine.  •   THE RESULT IS GROUPED BY THE VALUE YOU TYPED: every value gets its own block of lots with a shaded ∑ total row beneath it, then a blue TOTAL MATCHED row adds every group up at once - the grand total of the rows your search actually hit, sitting right beneath them.  Under that a greyed REMAINING block holds the lots that did not match, with its own total, and the green GRAND TOTAL of both sits at the foot.  A lot matching two values is counted under the first one only, so TOTAL MATCHED + REMAINING always equals GRAND TOTAL, and with nothing typed the matched row is the whole list.   •   clear the box and all 37 come back in one ALL LOTS block.   •   cell F3 narrows what the text is looked for in (lot no. + buyer + name by default).   •   matching is contains, not case sensitive.   •   nothing here is typed in: every figure is a live link to Final Calculation Sheet.   •   columns AK..CU are hidden helpers.   •   use the +/- outline control above columns D:H to expand/collapse Lot Name through Rate under Buyer.   •   type BLANK or (blank) in a search field to match empty cells.</t>
   </si>
   <si>
     <t>🔍  SEARCH  ▸</t>
@@ -6461,7 +6461,7 @@
         <v>1763 AL HAMD TRADE CORPORATION Lot No.</v>
       </c>
       <c r="AM5">
-        <f t="shared" ref="AM5:AM41" si="1">IF(COUNTIF($BM5:$CU5,0)&gt;0,0,IF($B$3="",1,IF(AND(IF(COUNTIF($AR$9:$AY$9,1)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=1)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,2)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=2)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,3)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=3)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,4)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=4)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,5)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=5)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,6)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=6)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,7)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=7)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0),IF(COUNTIF($AR$9:$AY$9,8)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=8)*($AR$6:$AY$6&lt;&gt;"")*ISNUMBER(SEARCH($AR$6:$AY$6,$AK5)))&gt;0)),1,0)))</f>
+        <f t="shared" ref="AM5:AM41" si="1">IF(COUNTIF($BM5:$CU5,0)&gt;0,0,IF($B$3="",1,IF(AND(IF(COUNTIF($AR$9:$AY$9,1)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=1)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,2)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=2)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,3)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=3)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,4)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=4)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,5)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=5)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,6)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=6)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,7)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=7)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0),IF(COUNTIF($AR$9:$AY$9,8)=0,TRUE,SUMPRODUCT(($AR$9:$AY$9=8)*($AR$6:$AY$6&lt;&gt;"")*IF(((UPPER($AR$6:$AY$6)="BLANK")+(UPPER($AR$6:$AY$6)="(BLANK)")+(UPPER($AR$6:$AY$6)="EMPTY")+(UPPER($AR$6:$AY$6)="(EMPTY)"))&gt;0,$AK5="",ISNUMBER(SEARCH($AR$6:$AY$6,$AK5))))&gt;0)),1,0)))</f>
         <v>0</v>
       </c>
       <c r="AO5" t="s">
@@ -6551,143 +6551,143 @@
         <v>0</v>
       </c>
       <c r="BM5">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN5">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO5">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP5">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ5">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR5">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS5">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT5">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU5">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV5">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW5">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX5">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY5">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ5">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA5">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB5">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC5">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD5">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE5">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF5">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG5">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH5">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI5">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ5">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK5">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL5">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM5">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN5">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO5">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP5">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ5">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR5">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS5">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT5">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$4)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU5">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$4&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$4&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$4&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -6923,143 +6923,143 @@
         <v>0</v>
       </c>
       <c r="BM6">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN6">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO6">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP6">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ6">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR6">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS6">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT6">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU6">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV6">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW6">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX6">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY6">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ6">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA6">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB6">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC6">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD6">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE6">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF6">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG6">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH6">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI6">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ6">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK6">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL6">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM6">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN6">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO6">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP6">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ6">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR6">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS6">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT6">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$5)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$5)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$5)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU6">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$5&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$5&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$5&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -7295,143 +7295,143 @@
         <v>0</v>
       </c>
       <c r="BM7">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN7">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO7">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP7">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ7">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR7">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS7">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT7">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU7">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV7">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW7">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX7">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY7">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ7">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA7">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB7">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC7">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD7">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE7">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF7">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG7">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH7">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI7">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ7">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK7">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL7">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM7">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN7">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO7">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP7">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ7">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR7">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS7">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT7">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$6)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$6)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$6)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU7">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$6&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$6&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$6&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -7666,143 +7666,143 @@
         <v>0</v>
       </c>
       <c r="BM8">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN8">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO8">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP8">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ8">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR8">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS8">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT8">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU8">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV8">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW8">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX8">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY8">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ8">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA8">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB8">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC8">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD8">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE8">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF8">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG8">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH8">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI8">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ8">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK8">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL8">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM8">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN8">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO8">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP8">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ8">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR8">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS8">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT8">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$7)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$7)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$7)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU8">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$7&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$7&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$7&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -8038,143 +8038,143 @@
         <v>0</v>
       </c>
       <c r="BM9">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN9">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO9">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP9">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ9">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR9">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS9">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT9">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU9">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV9">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW9">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX9">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY9">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ9">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA9">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB9">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC9">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD9">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE9">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF9">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG9">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH9">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI9">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ9">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK9">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL9">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM9">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN9">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO9">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP9">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ9">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR9">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS9">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT9">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$8)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$8)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$8)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU9">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$8&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$8&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$8&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -8375,143 +8375,143 @@
         <v>0</v>
       </c>
       <c r="BM10">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN10">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO10">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP10">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ10">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR10">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS10">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT10">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU10">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV10">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW10">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX10">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY10">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ10">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA10">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB10">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC10">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD10">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE10">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF10">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG10">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH10">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI10">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ10">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK10">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL10">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM10">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN10">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO10">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP10">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ10">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR10">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS10">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT10">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$9)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$9)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$9)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU10">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$9&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$9&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$9&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -8712,143 +8712,143 @@
         <v>0</v>
       </c>
       <c r="BM11">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN11">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO11">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP11">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ11">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR11">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS11">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT11">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU11">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV11">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW11">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX11">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY11">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ11">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA11">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB11">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC11">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD11">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE11">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF11">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG11">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH11">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI11">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ11">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK11">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL11">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM11">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN11">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO11">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP11">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ11">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR11">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS11">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT11">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$10)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$10)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$10)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU11">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$10&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$10&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$10&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -9049,143 +9049,143 @@
         <v>0</v>
       </c>
       <c r="BM12">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN12">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO12">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP12">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ12">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR12">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS12">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT12">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU12">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV12">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW12">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX12">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY12">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ12">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA12">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB12">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC12">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD12">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE12">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF12">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG12">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH12">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI12">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ12">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK12">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL12">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM12">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN12">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO12">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP12">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ12">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR12">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS12">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT12">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$11)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$11)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$11)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU12">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$11&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$11&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$11&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -9386,143 +9386,143 @@
         <v>0</v>
       </c>
       <c r="BM13">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN13">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO13">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP13">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ13">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR13">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS13">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT13">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU13">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV13">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW13">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX13">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY13">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ13">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA13">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB13">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC13">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD13">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE13">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF13">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG13">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH13">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI13">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ13">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK13">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL13">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM13">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN13">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO13">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP13">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ13">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR13">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS13">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT13">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$12)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$12)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$12)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU13">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$12&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$12&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$12&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -9711,143 +9711,143 @@
         <v>0</v>
       </c>
       <c r="BM14">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN14">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO14">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP14">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ14">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR14">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS14">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT14">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU14">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV14">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW14">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX14">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY14">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ14">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA14">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB14">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC14">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD14">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE14">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF14">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG14">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH14">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI14">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ14">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK14">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL14">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM14">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN14">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO14">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP14">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ14">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR14">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS14">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT14">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$13)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$13)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$13)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU14">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$13&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$13&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$13&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -10036,143 +10036,143 @@
         <v>0</v>
       </c>
       <c r="BM15">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN15">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO15">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP15">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ15">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR15">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS15">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT15">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU15">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV15">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW15">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX15">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY15">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ15">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA15">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB15">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC15">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD15">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE15">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF15">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG15">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH15">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI15">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ15">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK15">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL15">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM15">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN15">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO15">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP15">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ15">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR15">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS15">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT15">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$14)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$14)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$14)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU15">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$14&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$14&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$14&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -10361,143 +10361,143 @@
         <v>1</v>
       </c>
       <c r="BM16">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN16">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO16">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP16">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ16">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR16">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS16">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT16">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU16">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV16">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW16">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX16">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY16">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ16">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA16">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB16">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC16">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD16">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE16">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF16">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG16">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH16">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI16">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ16">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK16">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL16">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM16">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN16">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO16">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP16">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ16">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR16">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS16">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT16">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$15)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$15)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$15)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU16">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$15&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$15&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$15&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -10686,143 +10686,143 @@
         <v>0</v>
       </c>
       <c r="BM17">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN17">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO17">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP17">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ17">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR17">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS17">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT17">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU17">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV17">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW17">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX17">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY17">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ17">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA17">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB17">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC17">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD17">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE17">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF17">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG17">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH17">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI17">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ17">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK17">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL17">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM17">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN17">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO17">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP17">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ17">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR17">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS17">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT17">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$16)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$16)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$16)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU17">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$16&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$16&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$16&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -11011,143 +11011,143 @@
         <v>0</v>
       </c>
       <c r="BM18">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN18">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO18">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP18">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ18">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR18">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS18">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT18">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU18">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV18">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW18">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX18">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY18">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ18">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA18">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB18">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC18">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD18">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE18">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF18">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG18">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH18">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI18">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ18">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK18">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL18">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM18">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN18">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO18">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP18">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ18">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR18">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS18">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT18">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$17)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$17)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$17)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU18">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$17&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$17&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$17&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -11336,143 +11336,143 @@
         <v>0</v>
       </c>
       <c r="BM19">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN19">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO19">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP19">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ19">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR19">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS19">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT19">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU19">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV19">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW19">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX19">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY19">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ19">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA19">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB19">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC19">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD19">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE19">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF19">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG19">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH19">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI19">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ19">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK19">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL19">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM19">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN19">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO19">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP19">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ19">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR19">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS19">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT19">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$18)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$18)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$18)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU19">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$18&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$18&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$18&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -11661,143 +11661,143 @@
         <v>0</v>
       </c>
       <c r="BM20">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN20">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO20">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP20">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ20">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR20">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS20">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT20">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU20">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV20">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW20">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX20">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY20">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ20">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA20">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB20">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC20">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD20">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE20">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF20">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG20">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH20">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI20">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ20">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK20">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL20">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM20">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN20">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO20">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP20">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ20">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR20">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS20">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT20">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$19)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$19)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$19)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU20">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$19&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$19&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$19&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -11986,143 +11986,143 @@
         <v>0</v>
       </c>
       <c r="BM21">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN21">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO21">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP21">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ21">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR21">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS21">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT21">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU21">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV21">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW21">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX21">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY21">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ21">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA21">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB21">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC21">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD21">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE21">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF21">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG21">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH21">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI21">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ21">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK21">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL21">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM21">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN21">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO21">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP21">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ21">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR21">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS21">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT21">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$20)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$20)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$20)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU21">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$20&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$20&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$20&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -12311,143 +12311,143 @@
         <v>0</v>
       </c>
       <c r="BM22">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN22">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO22">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP22">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ22">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR22">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS22">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT22">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU22">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV22">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW22">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX22">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY22">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ22">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA22">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB22">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC22">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD22">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE22">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF22">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG22">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH22">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI22">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ22">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK22">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL22">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM22">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN22">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO22">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP22">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ22">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR22">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS22">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT22">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$21)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$21)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$21)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU22">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$21&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$21&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$21&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -12636,143 +12636,143 @@
         <v>0</v>
       </c>
       <c r="BM23">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN23">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO23">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP23">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ23">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR23">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS23">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT23">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU23">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV23">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW23">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX23">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY23">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ23">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA23">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB23">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC23">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD23">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE23">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF23">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG23">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH23">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI23">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ23">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK23">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL23">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM23">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN23">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO23">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP23">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ23">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR23">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS23">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT23">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$22)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$22)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$22)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU23">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$22&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$22&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$22&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -12961,143 +12961,143 @@
         <v>0</v>
       </c>
       <c r="BM24">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN24">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO24">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP24">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ24">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR24">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS24">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT24">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU24">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV24">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW24">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX24">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY24">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ24">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA24">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB24">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC24">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD24">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE24">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF24">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG24">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH24">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI24">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ24">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK24">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL24">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM24">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN24">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO24">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP24">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ24">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR24">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS24">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT24">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$23)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$23)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$23)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU24">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$23&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$23&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$23&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -13286,143 +13286,143 @@
         <v>0</v>
       </c>
       <c r="BM25">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN25">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO25">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP25">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ25">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR25">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS25">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT25">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU25">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV25">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW25">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX25">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY25">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ25">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA25">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB25">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC25">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD25">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE25">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF25">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG25">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH25">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI25">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ25">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK25">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL25">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM25">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN25">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO25">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP25">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ25">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR25">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS25">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT25">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$24)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$24)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$24)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU25">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$24&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$24&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$24&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -13611,143 +13611,143 @@
         <v>0</v>
       </c>
       <c r="BM26">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN26">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO26">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP26">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ26">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR26">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS26">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT26">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU26">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV26">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW26">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX26">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY26">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ26">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA26">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB26">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC26">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD26">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE26">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF26">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG26">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH26">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI26">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ26">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK26">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL26">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM26">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN26">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO26">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP26">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ26">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR26">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS26">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT26">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$25)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$25)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$25)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU26">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$25&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$25&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$25&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -13936,143 +13936,143 @@
         <v>0</v>
       </c>
       <c r="BM27">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN27">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO27">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP27">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ27">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR27">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS27">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT27">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU27">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV27">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW27">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX27">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY27">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ27">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA27">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB27">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC27">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD27">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE27">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF27">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG27">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH27">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI27">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ27">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK27">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL27">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM27">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN27">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO27">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP27">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ27">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR27">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS27">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT27">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$26)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$26)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$26)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU27">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$26&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$26&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$26&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -14261,143 +14261,143 @@
         <v>0</v>
       </c>
       <c r="BM28">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN28">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO28">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP28">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ28">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR28">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS28">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT28">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU28">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV28">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW28">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX28">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY28">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ28">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA28">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB28">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC28">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD28">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE28">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF28">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG28">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH28">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI28">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ28">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK28">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL28">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM28">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN28">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO28">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP28">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ28">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR28">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS28">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT28">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$27)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$27)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$27)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU28">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$27&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$27&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$27&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -14586,143 +14586,143 @@
         <v>0</v>
       </c>
       <c r="BM29">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN29">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO29">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP29">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ29">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR29">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS29">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT29">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU29">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV29">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW29">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX29">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY29">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ29">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA29">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB29">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC29">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD29">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE29">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF29">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG29">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH29">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI29">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ29">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK29">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL29">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM29">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN29">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO29">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP29">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ29">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR29">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS29">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT29">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$28)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$28)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$28)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU29">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$28&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$28&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$28&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -14911,143 +14911,143 @@
         <v>0</v>
       </c>
       <c r="BM30">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN30">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO30">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP30">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ30">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR30">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS30">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT30">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU30">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV30">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW30">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX30">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY30">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ30">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA30">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB30">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC30">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD30">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE30">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF30">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG30">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH30">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI30">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ30">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK30">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL30">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM30">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN30">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO30">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP30">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ30">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR30">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS30">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT30">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$29)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$29)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$29)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU30">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$29&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$29&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$29&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -15236,143 +15236,143 @@
         <v>0</v>
       </c>
       <c r="BM31">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN31">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO31">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP31">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ31">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR31">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS31">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT31">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU31">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV31">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW31">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX31">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY31">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ31">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA31">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB31">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC31">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD31">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE31">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF31">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG31">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH31">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI31">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ31">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK31">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL31">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM31">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN31">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO31">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP31">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ31">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR31">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS31">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT31">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$30)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$30)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$30)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU31">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$30&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$30&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$30&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -15561,143 +15561,143 @@
         <v>0</v>
       </c>
       <c r="BM32">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN32">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO32">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP32">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ32">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR32">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS32">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT32">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU32">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV32">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW32">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX32">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY32">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ32">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA32">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB32">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC32">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD32">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE32">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF32">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG32">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH32">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI32">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ32">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK32">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL32">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM32">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN32">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO32">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP32">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ32">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR32">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS32">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT32">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$31)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$31)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$31)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU32">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$31&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$31&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$31&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -15886,143 +15886,143 @@
         <v>0</v>
       </c>
       <c r="BM33">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN33">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO33">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP33">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ33">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR33">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS33">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT33">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU33">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV33">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW33">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX33">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY33">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ33">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA33">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB33">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC33">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD33">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE33">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF33">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG33">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH33">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI33">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ33">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK33">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL33">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM33">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN33">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO33">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP33">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ33">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR33">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS33">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT33">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$32)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$32)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$32)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU33">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$32&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$32&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$32&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -16211,143 +16211,143 @@
         <v>0</v>
       </c>
       <c r="BM34">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN34">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO34">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP34">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ34">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR34">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS34">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT34">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU34">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV34">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW34">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX34">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY34">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ34">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA34">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB34">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC34">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD34">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE34">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF34">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG34">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH34">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI34">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ34">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK34">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL34">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM34">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN34">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO34">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP34">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ34">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR34">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS34">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT34">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$33)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$33)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$33)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU34">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$33&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$33&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$33&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -16536,143 +16536,143 @@
         <v>0</v>
       </c>
       <c r="BM35">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN35">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO35">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP35">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ35">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR35">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS35">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT35">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU35">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV35">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW35">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX35">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY35">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ35">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA35">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB35">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC35">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD35">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE35">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF35">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG35">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH35">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI35">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ35">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK35">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL35">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM35">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN35">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO35">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP35">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ35">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR35">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS35">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT35">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$34)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$34)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$34)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU35">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$34&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$34&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$34&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -16861,143 +16861,143 @@
         <v>0</v>
       </c>
       <c r="BM36">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN36">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO36">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP36">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ36">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR36">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS36">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT36">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU36">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV36">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW36">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX36">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY36">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ36">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA36">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB36">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC36">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD36">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE36">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF36">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG36">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH36">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI36">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ36">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK36">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL36">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM36">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN36">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO36">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP36">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ36">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR36">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS36">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT36">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$35)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$35)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$35)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU36">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$35&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$35&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$35&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -17186,143 +17186,143 @@
         <v>0</v>
       </c>
       <c r="BM37">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN37">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO37">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP37">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ37">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR37">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS37">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT37">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU37">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV37">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW37">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX37">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY37">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ37">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA37">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB37">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC37">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD37">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE37">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF37">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG37">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH37">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI37">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ37">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK37">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL37">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM37">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN37">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO37">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP37">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ37">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR37">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS37">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT37">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$36)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$36)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$36)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU37">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$36&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$36&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$36&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -17511,143 +17511,143 @@
         <v>0</v>
       </c>
       <c r="BM38">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN38">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO38">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP38">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ38">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR38">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS38">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT38">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU38">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV38">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW38">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX38">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY38">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ38">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA38">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB38">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC38">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD38">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE38">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF38">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG38">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH38">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI38">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ38">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK38">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL38">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM38">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN38">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO38">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP38">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ38">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR38">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS38">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT38">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$37)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$37)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$37)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU38">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$37&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$37&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$37&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -17836,143 +17836,143 @@
         <v>0</v>
       </c>
       <c r="BM39">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN39">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO39">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP39">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ39">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR39">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS39">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT39">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU39">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV39">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW39">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX39">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY39">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ39">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA39">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB39">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC39">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD39">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE39">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF39">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG39">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH39">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI39">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ39">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK39">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL39">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM39">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN39">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO39">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP39">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ39">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR39">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS39">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT39">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$38)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$38)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$38)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU39">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$38&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$38&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$38&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -18161,143 +18161,143 @@
         <v>0</v>
       </c>
       <c r="BM40">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN40">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO40">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP40">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ40">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR40">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS40">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT40">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU40">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV40">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW40">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX40">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY40">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ40">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA40">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB40">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC40">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD40">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE40">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF40">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG40">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH40">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI40">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ40">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK40">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL40">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM40">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN40">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO40">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP40">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ40">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR40">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS40">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT40">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$39)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$39)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$39)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU40">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$39&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$39&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$39&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -18486,143 +18486,143 @@
         <v>0</v>
       </c>
       <c r="BM41">
-        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"",""))))&gt;0))</f>
+        <f>IF($A$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((ROW()-4)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($A$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((ROW()-4)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BN41">
-        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($B$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$F$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($B$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$F$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BO41">
-        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($C$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$G$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($C$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$G$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BP41">
-        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($D$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$B$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($D$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$B$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BQ41">
-        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($E$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$D$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($E$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$D$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BR41">
-        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($F$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$A$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($F$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$A$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BS41">
-        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($G$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$E$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($G$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$E$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BT41">
-        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($H$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$C$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($H$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$C$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BU41">
-        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($I$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$H$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($I$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$H$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BV41">
-        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($J$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$I$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($J$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$I$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BW41">
-        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($K$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$J$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($K$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$J$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BX41">
-        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($L$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$K$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($L$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$K$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BY41">
-        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($M$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$L$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($M$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$L$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="BZ41">
-        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($N$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$M$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($N$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$M$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CA41">
-        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($O$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$N$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($O$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$N$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CB41">
-        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($P$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$O$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($P$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$O$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CC41">
-        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($Q$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$P$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Q$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$P$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CD41">
-        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($R$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Q$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($R$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Q$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CE41">
-        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($S$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$R$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($S$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$R$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CF41">
-        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($T$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$S$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($T$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$S$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CG41">
-        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($U$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$T$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($U$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$T$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CH41">
-        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($V$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$U$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($V$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$U$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CI41">
-        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($W$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$V$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($W$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$V$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CJ41">
-        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($X$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$W$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($X$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$W$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CK41">
-        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($Y$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$X$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Y$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$X$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CL41">
-        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($Z$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Y$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($Z$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Y$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CM41">
-        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AA$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$Z$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AA$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$Z$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CN41">
-        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AB$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AA$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AB$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AA$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CO41">
-        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AC$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AB$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AC$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AB$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CP41">
-        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AD$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AC$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AD$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AC$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CQ41">
-        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AE$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AD$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AE$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AD$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CR41">
-        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AF$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AE$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AF$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AE$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CS41">
-        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AG$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AF$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AG$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AF$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CT41">
-        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$40)&amp;"",""))))&gt;0))</f>
+        <f>IF($AH$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR(('Final Calculation Sheet'!$AG$40)&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AH$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR(('Final Calculation Sheet'!$AG$40)&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
       <c r="CU41">
-        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$40&lt;=0,"SETTLED","OUTSTANDING"))&amp;"",""))))&gt;0))</f>
+        <f>IF($AI$4="",1,--(SUMPRODUCT(--(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99))&lt;&gt;""),--IF(((UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="BLANK")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(BLANK)")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="EMPTY")+(UPPER(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)))="(EMPTY)"))&gt;0,IFERROR((IF('Final Calculation Sheet'!$AD$40&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")="",ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE(SUBSTITUTE($AI$4,"/",","),",",REPT(" ",99)),(ROW($1:$8)-1)*99+1,99)),IFERROR((IF('Final Calculation Sheet'!$AD$40&lt;=0,"SETTLED","OUTSTANDING"))&amp;"","")))))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
@@ -20764,7 +20764,7 @@
     <dataValidation type="list" sqref="F3" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$AO$4:$AO$9</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="A4:AI4" promptTitle="Column wildcard search" prompt="Type text; comma or / means ANY. Use * for any text or ? for one character.">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="A4:AI4" promptTitle="Column wildcard search" prompt="Type text; comma or / means ANY. Use * or ? wildcards. Use BLANK or (blank) for empty cells.">
       <formula1>1=1</formula1>
     </dataValidation>
   </dataValidations>
